--- a/Data/7052019-09062024/Split_Data/with_account/Scraped_Results/Open VLD_official.xlsx
+++ b/Data/7052019-09062024/Split_Data/with_account/Scraped_Results/Open VLD_official.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>hearts_count</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>transcription</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -481,10 +486,8 @@
           <t>robbydecaluwe</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7374706022042193185</t>
-        </is>
+      <c r="B2" t="n">
+        <v>7.374706022042193e+18</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -504,16 +507,13 @@
           <t>Minder regels en eenvoudigere vergunningen! Zo houden we bedrijven in eigen land, zorgen we voor werkzekerheid en kunnen er meer mensen aan de slag.  Dat is essentieel voor onze welvaart.  Werken doen lonen Morgen doen werken</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>robbydecaluwe</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1033</v>
-      </c>
-      <c r="I2" t="n">
-        <v>20</v>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -522,10 +522,8 @@
           <t>robbydecaluwe</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7363576696194256160</t>
-        </is>
+      <c r="B3" t="n">
+        <v>7.363576696194256e+18</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -541,16 +539,13 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>robbydecaluwe</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>965</v>
-      </c>
-      <c r="I3" t="n">
-        <v>39</v>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -559,10 +554,8 @@
           <t>robbydecaluwe</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>7362591366364319009</t>
-        </is>
+      <c r="B4" t="n">
+        <v>7.362591366364319e+18</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,16 +575,13 @@
           <t>Gisteren bracht ik samen met Jean-Jacques De Gucht een interessant bezoek aan het abortuscentrum Luna in Gent.  Experten zijn duidelijk: 1️⃣ De termijn waarbinnen een abortus mogelijk moet zijn, moet naar 18 weken worden uitgebreid. Nu is dat 12 weken. Vrouwen die bijvoorbeeld pas laat ontdekken dat ze zwanger zijn, moeten nu naar het buitenland. Jaarlijks zijn er 300 tot 500 vrouwen die naar het buitenland gaan om een abortus te laten uitvoeren. Dat is heel erg stigmatiserend, en ze moeten daardoor ook alle kosten zelf betalen. Die bedragen tot 1.500 EUR. 2️⃣ De verplichte wachttijd van 6 dagen moet worden afgeschaft. Een vrouw die naar een abortuscentrum gaat, heeft al nagedacht over hoe ze met haar ongeplande zwangerschap wil omgaan. Die zes dagen hebben dus geen enkel nut en zorgen voor een nodeloze mentale druk. 3️⃣ De verplichting om vrouwen te wijzen op adoptie, alsof dat een alternatief is voor een abortus bij een ongeplande zwangerschap, moet ook uit de wet. Wist je trouwens dat ons land volgens de WHO tot de landen met het laagste abortuscijfer behoort? Dat komt onder andere doordat we in ons land sterk inzetten op anticonceptie. Maar ook anticonceptie is niet onfeilbaar. Meer dan de helft van de vrouwen die ongepland zwanger werden en voor een abortus kiezen, gebruikte anticonceptie.  Open Vld pleit er bovendien voor om zelfbeschikking (en dus oa het recht op abortus) in de grondwet op te nemen. Want overal in Europa zien we dat deze zelfbeschikking onder druk staat door extreemrechtse conservatieve krachten. Dank aan Katja Gabriëls die hiervoor de afgelopen 5 jaar binnen het parlement is blijven strijden.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>robbydecaluwe</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>2576</v>
-      </c>
-      <c r="I4" t="n">
-        <v>71</v>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -600,10 +590,8 @@
           <t>robbydecaluwe</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7356987700043468064</t>
-        </is>
+      <c r="B5" t="n">
+        <v>7.356987700043468e+18</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -623,16 +611,13 @@
           <t>Kunnen bellen en toegang tot het internet zouden vandaag vanzelfsprekend moeten zijn, maar is het niet. Céline Vermeiren (2de opvolger Kamer in Oost-Vlaanderen) en ik kaarten dit probleem aan. #nmbs #wifiopdetrein #treinreizen</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>robbydecaluwe</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>5642</v>
-      </c>
-      <c r="I5" t="n">
-        <v>94</v>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -641,10 +626,8 @@
           <t>robbydecaluwe</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>7341138726849875233</t>
-        </is>
+      <c r="B6" t="n">
+        <v>7.341138726849875e+18</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -664,16 +647,5125 @@
           <t>4,9 jaar. Zo lang moeten mensen die aan een zeldzame ziekte lijden gemiddeld wachten op hun diagnose.  Veel te lang. Dat moet beter.  Tijd dat we patiënten perspectief geven. Hoe sneller de diagnose, hoe sneller de geschikte medicatie kan worden toegediend.  #RareDiseaseDay</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>robbydecaluwe</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>468</v>
-      </c>
-      <c r="I6" t="n">
-        <v>20</v>
+      <c r="B7" t="n">
+        <v>7.339514082883554e+18</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robbydecaluwe/video/7339514082883554593</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1708863793</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024-02-25 04:23:13</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mars voor vrede - Tegen onderdrukking, voor vrijheid #ukraine #oekraine 🇺🇦</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>robbydecaluwe</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7.249461522919853e+18</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robbydecaluwe/video/7249461522919853339</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1687896853</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2023-06-27 13:14:13</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>België keurt verbod op convesietherapie of 'homogenezing' goed. En dat is een goede zaak. We staan momenteel op de tweede plaats van de Rainbow Index als LGBTI+-vriendelijk land. Het moet onze ambitie zijn om op de eerste plaats te staan, en daar kan deze wet ons bij helpen. Dank aan collega Katja Gabriëls om hier in de commissie justitie mee voor aan de kar te trekken. #lgbtqi#lgbti#gelijkekansen#dekamer#lachambre #conversietherapie #openvld</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>robbydecaluwe</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7.234226647208152e+18</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robbydecaluwe/video/7234226647208152346</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1684349654</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2023-05-17 11:54:14</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Omdat de strijd voor gelijke rechten nog niet gestreden is. Omdat lqbtqi+-personen nog altijd met geweld te maken hebben. #idahot #LoveIsLove</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>robbydecaluwe</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7.196275430129733e+18</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robbydecaluwe/video/7196275430129732870</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1675513447</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2023-02-04 04:24:07</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Of je nu conservatief, progressief, katholiek of vrijzinnig bent: het recht op euthanasie is een verworven recht dat ons niet meer mag worden afgepakt! Mee eens? #openvld #euthanasie</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>robbydecaluwe</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7.159430300840283e+18</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robbydecaluwe/video/7159430300840283397</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1666934774</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2022-10-27 22:26:14</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Voortaan kunnen verzekeraars aan mensen die bvb genezen zijn van kanker niet langer een verzekering gewaarborgd inkomen weigeren.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>robbydecaluwe</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7.099914392657055e+18</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robbydecaluwe/video/7099914392657054982</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1653077640</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2022-05-20 13:14:00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>#idahot #lgbtqi+ #pride2022🏳️‍🌈</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>robbydecaluwe</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7.034642552854695e+18</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robbydecaluwe/video/7034642552854695174</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1637880354</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2021-11-25 14:45:54</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>#stopgeweldtegenvrouwen</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7.377285903586299e+18</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7377285903586299169</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1717658234</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2024-06-06 00:17:14</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>🚜</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7.376649243597016e+18</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7376649243597016353</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1717509999</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2024-06-04 07:06:39</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Wake-up call 📞</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>en weet u wat wake-up Call Vlaardingen heette niet alleen Johan Vlamingen heet ook mooi of meer een en nu zou blij moeten zijn Ik ga eerst beginnen met de zeggen dat ik uw taal gebruik over dit soort zaken eh over de volledige lijn afkeur op de volledige lijnen achter u spreekt over een tsunami het gaat hierover mensen en weet u wat Wake Up Call en 2024 Vlamingen zijn niet alleen wiet Vlamingen heette niet alleen Johan VL dit ook mooi of met een en nu zou blij moeten zijn dat Vlaanderen groeit meneer dat is het eerste dat je zegt zijn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7.376279648679857e+18</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7376279648679857441</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1717423947</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2024-06-03 07:12:27</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Menstruatieproducten toegankelijk maken voor iedereen. Wat denk jij? 👇</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Wat is jou opgevallen ehm een bericht van meester Rutte die in de toiletten van de Vlaamse regering overal gratis tampons een maandverband zal eh leggen ze mag de vergelijking we vragen mannen toch ook niet om een eigen wc-rolletje mee te nemen Ik vind dat een super goede vergelijking Eigenlijk zou maandverband en tampons overal gewoon een Alle toiletten openbaar hier Backstage eh overal zouden moeten liggen als er gratis wc-papier is dan zouden daar ook gratis verband moeten eh lichtje Maar ja een paar bedrijven met heel veel werknemers vrouwelijke werknemers ook goed idee dus ze brengt het jou op idee of doen jullie het al misschien nee we doen het niet maar heel Simpelweg 50 vind ik dat ze volledig gelijk heeft het is de eerste stap naar echt mannen en vrouwen gelijkwaardigheid dat is eigenlijk de de eigenlijk super normaal dat dat zou niet eens om dat altijd mannen zijn die daarover beslist Staat waarschijnlijk absoluut</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7.37545360409153e+18</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7375453604091530528</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1717231616</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2024-06-01 01:46:56</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>🫧 Brabant doen bruisen 🫧</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Vlaams Brabant Hier is het goede leven uitgevonden in het land van bier braadworst en Breugel hier ontstond 600 jaar geleden de oudste Universiteit van het land hier open de luchthaven een venster op de wereld Hier zit er in Vlaanderen wereldwijd op de festival kaart hiervoor de suikerklontjes gemaakt in vlaams-brabant zijn de bossen nog wouden heeft Urbanus een standbeeld en islamique een bier trip View vanuit vlaams-brabant stroop de grootste Belg naar molokai veroverde wielrenners en veldrijden is de Harten en veranderde we de wereld op het vlak van microtechnologie hier koesteren we onze abdijen en kasteelen hier werken als Brabantse trekpaarden wie we ook zijn en van Waren we ook komen wat we ook doen een ding hebben we allemaal geleerd we willen Brabant doen Pruis</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7.375131018501705e+18</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7375131018501704992</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1717156512</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2024-05-31 04:55:12</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Klink 👏 klare 👏 onzin.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dat is voor wat mij betreft klink Clare racistische onzin Ik had mijn voorgenomen om mij niet te laten provoceren Ik ga dat niet doen we gaan elkaar op dat u nooit overtuigen hè Maar ik kan toch ook niet zwijgen als ik dergelijke onzin hoor dus ik ga er wel op zeggen dat ik u aanraad om uh eh DNA in te laten analyseren om verbaasde staan wat er in uw DNA allemaal zal zitten en dat dat u zal vertellen over dat is het eerste dus die definitie van omvolking het nu heb ik het woord in de mond genomen die ik deel dat absoluut niet ten tweede als u het hebt over cultuur dan kan ik er meteen zeggen dat uw cultuur de mijne niet eens We delen die niet Ik deel geen extremistische Vlaams nationalistische cultuur kunt gedaan en dus zeggen dat je op basis daarvan dit soort theorieën kan vertolken dat is voor wat mij betreft klink klaar racistische onzin</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>7.374741936197979e+18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7374741936197979424</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1717065919</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2024-05-30 03:45:19</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Toegankelijke winkels voor mensen met een beperking. @Carrefourbe geeft het goede voorbeeld 🙌</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>We zijn hier aan de Carrefour in Oudergem en zij zijn de aller eerste winkel van België die winkelen ook mogelijk maakt voor mensen met een visuele beperking mijn naam is Herman collier ik ben voorzitter van blindenzorg licht en liefde stel u voor iemand verliest en zegt Wij proberen die dus een leven dus terug op de rails te krijgen hè dus ook op digitale gebied mensen kunnen cursussen volgen hoe dat ze met kunnen omgaan met verschillende applicaties en apps nu vandaag in de Carrefour hebben we dus Navy lens gebruikt om onze weg te vinden naar bepaalde producten dat is mij gelukt met wel wat moeilijkheden maar ja ik heb Navy lens maar gedownload van eergisteren Dus er is nog veel leren aan dat is heel belangrijk voor Carrefour maar dat is eigenlijk heel belangrijk voor alle organisaties en bedrijven een nu maar ook als zij iets bouwen of dat iets maakt rekening houden met iedereen dus ook voor mensen met een beperking daar rekening mee houden vanaf de conceptfase en dan ga je minder kosten hebben om het toegankelijk te maken van dan heb je er al van een begin meer rekening gehouden dat drukte kosten naar beneden</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7.374695299576548e+18</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7374695299576548640</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1717055062</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2024-05-30 00:44:22</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Leef en laat leven. Stem @OpenVld 💙</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>de belangrijkste waarde voor mijn partij is vrijheid dat jij de keuzes kan maken kan zijn wie je bent dat je niet teveel regels nodig hebt maar wel twee dingen ook verantwoordelijkheid en verdraagzaamheid want fruit wil ik niet zeggen dat wat jij wil dat iedereen dat moet doen leven en laten leven stemmen open beelden</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7.374380632044047e+18</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7374380632044047648</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1716981797</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2024-05-29 04:23:17</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>🏳️‍🌈🏳️‍🌈🏳️‍🌈</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Wat een onzin is me dat hè Het begint met lachen met mensen en het eindigt dan niet meer hand in hand durven lopen op straat geven als je ziet dat mensen ehm ja geraakt worden in deze zijn niet zichzelf kunnen zijn geconfronteerd worden met discriminatie dan ga ik daar niet ligt overheen en dan ga ik zeker niet zoals eh Tom Van Grieken gisteren in één van de uitzendingen zei ze zeggen dat je wel mag lachen met mensen en dat je er maar moet tegen kunnen Wat een onzin is me dat hè Het begint met lachen met mensen en het eindigt een nieuwe verhaaltje van het lopen besteld dus dat is een Nobel</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7.374035612011089e+18</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7374035612011089185</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1716901464</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2024-05-28 06:04:24</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Het recht op abortus zou in de grondwet moeten staan👇</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>uiteindelijk was het Grundel en Rutte die meer indruk leek te maken zij wilde het recht op haar bord is zelfs in de Grondwet Ik vind toch dat dat het aller eerste artikel zou moeten zijn van onze grondwet Ik vind de Grondwet die begint met België is een federale staat dat gaat over instellingen dat gaat over structuren dan gaan we over staat er vormingen dat is een politie die met zichzelf bezig zijn Laat de grond uit gaan over de mensen van dit land en het feit als het recht hebben om eh voor zichzelf op te komen en te zijn wie ze willen zijn bedankt alsjeblieft Ik was wel echt blij dat ze zei van ik wil dan nummer Artikel 1 in de Grondwet dan maakt hij wel duidelijk dat ze echt voor was en echt iets wat doen eraan ik zou stem op de Open Vld omdat ik denk dat zij het meest meedenken met de vernieuwende samenleving en dat ze het meest tanken met de jongeren</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7.373226640962309e+18</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7373226640962309408</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1716713115</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2024-05-26 01:45:15</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Averbode. Meer dan 900 jaar erfgoed om voor te strijden 💙</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>salut Rara waar ben ik op de lekdreef in Averbode met op de achtergrond en het was hier vandaag gewonnen fantastische dag met rommelmarkt heel veel leuke gesprekken en nu gaan we nog even Dag zeggen bij de Pater</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7.370285333247806e+18</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7370285333247806753</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1716028286</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2024-05-18 03:31:26</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Samen strijden tegen discriminatie 🏳️‍🌈#IDAHOT #PROLEAGUE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Het is vandaag Eye de god dat is de internationale dag tegen homofobie en transfobie en we zijn hier in het stadion van Union de helft ongeveer van de mensen die Belgen durft niet hand in hand op straat lopen als ze van hetzelfde geslacht zijn en het onderzoek blijkt dat het in de sport nog erger is dat sporters en voetballer is er niet voor durven uitkomen dat ze tot de lgbtqi gemeenschap behoorlijk dat kan natuurlijk niet en dus voor we actie niet alleen met woorden maar ook met daden in dit geval met een hele praktische gids voor voetbalclubs om aan de slag te gaan en inclusief te wegwerken</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7.361034658290601e+18</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7361034658290601249</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1713874443</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2024-04-23 05:14:03</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bedankt voor de interessante gesprekken ✌️ #openvld #verkiezingen #parlement</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>124 / 6263</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7.358740236521786e+18</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7358740236521786657</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1713340241</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2024-04-17 00:50:41</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Training met Bienvenu Boyata &amp; @Maurits Vande Reyde ⚽️ #Boyata #Aarschot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>snelheid aan de actie nee nemen binnen die bal gaat binnen oh oh oh oh we staan hier op het voetbalveld op de laag zitten in Aarschot deze twee gaan laten zien wat ze kunnen bij De trainingen van scha en rail The Double Down respect maat join mijn naam is says of the even plassen voor vlam Baba</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>7.332045251072331e+18</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7332045251072331040</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1707124833</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2024-02-05 01:20:33</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Het START.huis geeft je vleugels 🪽</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>leegstand tegengaan en tegelijkertijd beginnende ondernemers helpen dat is de perfecte combinatie met projecten zoals dit start huis investeert Vlaanderen en projecten van morgen in Marokko Ik heb hier een restaurant kan jij hier komen die drinken dat je een eten de stand huis heb ik met je hoofdpunt eh met je boekje houden en ook met eh materiaal hier te vinden voor mij keuken hier in de zaal Mijn droom is de zinnen een paar jaar eh meer restaurant Marokkaanse restaurant eh geven hier binnen voor de in Brussel en eh ik heb misschien Waarom niet in de in Antwerpen ook er is hier in Vilvoorde diverse en ondernemend Talent genoeg Het is alleen de kans geven om hun vleugels uit te slaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7.330711469060836e+18</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7330711469060836640</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1706814275</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2024-02-01 11:04:35</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mijn nieuwe poecast TABOELA RASA met @Evi Hanssen staat nu online!</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>zeg maar Juist ja Ja het is genoeg iets plastisch hè dus als mensen nu al Aanstoot nemen luister niet verder ik durf er ook over praten en ik hoop ook dat dat we er andere mee kunnen helpen en ik wil ook heel graag een beleid rond voeren Wauw Bam dat is uw lichaam dat dat doet dat is een mega natuurlijk proces we krijgen zelfs geen luxe je vochtige doekjes bij en er is een woord voor ja ja ja van eh anxiety and Hangover Ja ik me niks maar mensen hebben nu de neiging om aangelegen tegen mij hoeveel zijn 3 Heel hartelijk bedankt en veel succes dankjewel</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>gwendolynrutten</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>7.330282239755816e+18</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwendolynrutten/video/7330282239755816225</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1706714338</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2024-01-31 07:18:58</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>@Colruyt Group geeft het goede voorbeeld 👏</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>de werkplek Dat is een perfecte plaats om juist niet komen te integreren En dat hebben ze hier bij Colruyt perfect begrepen Colruyt gaat echt op zoek naar mensen medewerkers en voor hem te werken en tegelijkertijd bieden zijn aan om hier Talens te volgen naast heel veel andere opleidingen leren ze hier in het Nederlands al doende het is niet alleen op de schoolbanken maar gewoon ook in de praktijk Ik heb altijd Afghanistan om 8 uur 30 Ik ga naar de school en uh school Ik ga hier werken Ik heb wat daar vraag je dan Ik wil magazijn doen en dan samen met mijn begeleider spreken en samen met haar komen ik graag hier hoor ik hem om dat te zijn mijn allerlei collega over en de leuke of ik ben altijd blij met eh mijn alle collega's hier bij Colruyt hebben ze het begrepen hè werken de taal leren geen tijd te verliezen we zouden het heel fijn vinden als ze heel veel bedrijven in Vlaanderen om dezelfde je aan het werk gaan En daarom zetten we vanuit de Vlaamse regering een turbo op dit beleid wat ik hier vandaag heb gezien is echt zo belangrijk want</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>gwennydevroe</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7.346468686120619e+18</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@gwennydevroe/video/7346468686120619296</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1710483043</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2024-03-14 23:10:43</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Let's Go Ahead</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>steven.coenegrach</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>7.355516363286351e+18</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@steven.coenegrach/video/7355516363286351137</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1712589618</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2024-04-08 08:20:18</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>#openvld  #verkiezingen  #morgendoenwerken</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>denk vooral na over je stem en zorg ik dat je op een eh goed geïnformeerde gedegen manier aan die stembus eh komt en je stem uitbrengt want je stem telt wel degelijk ook na 9 juni</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>steven.coenegrach</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>7.337577013600964e+18</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@steven.coenegrach/video/7337577013600963872</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1708412799</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2024-02-19 23:06:39</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>🎥 TVLimburg vroeg mijn mening over de 32-uren werkweek. Een voorstel van PS. 🧑‍🏭🤝👨‍👩‍👧 werk en privé beter in evenwicht brengen is een uitdaging waar we allemaal aan moeten en willen werken. ❌ dit voorstel is echter los van alle realiteit. Het is onhaalbaar en onbetaalbaar.  💡PS zou beter samen met ons nadenken over het invullen van al die openstaande vacatures. Hoe krijg je werklozen geactiveerd? Bedrijven vinden vandaag geen personeel en dat verhoogt de werkdruk op de mensen die wél gaan werken. Daar ligt voor ons de oplossing. #ps  #openvld  #werk  #family</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Ik heb totaal onrealistisch voorstel positief dat mensen nadenken over hoe je werk en privé beter met mekaar kan eh kan combineren maar dit is een voorstel dat totaal los staat van de realiteit op de arbeidsmarkt vandaag het is zeer populistische Het is eh bijna erger dan verkiezingsbelofte ze dus eh los van de realiteit en ik denk dat het de populisten van P van de a n n n n lopen december dus heel jammer Ik hoop op een serieuzer debat te komen de maan</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>steven.coenegrach</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7.336864968190512e+18</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@steven.coenegrach/video/7336864968190512416</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1708247003</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2024-02-18 01:03:23</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>🏡 Hoe wij de woningmarkt weer betaalbaar willen maken? Bouwen, bouwen, bouwen. Alleen door meer kwalitatief aanbod worden de prijzen op de koop- en huurmarkt weer behapbaar.  Lees er alles over in ons woonplan:  https://www.openvld.be/woonplan#:~:text=Tegen%202035%20zullen%20er%20zo,kans%20hebben%20op%20de%20woningmarkt.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>steven.coenegrach</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>7.328728553002896e+18</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@steven.coenegrach/video/7328728553002896672</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1706352594</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2024-01-27 02:49:54</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>#bestepoliticus  #slechtstepoliticus  #limburg  #tvl  #verkiezingen  #5</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>die kussen van Limburg en maakt het een lijstje van de top 5 fronst even koenigs lijsttrekker voor de kamer bij Open Vld 7% tegenover 4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>steven.coenegrach</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>7.32540910180929e+18</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@steven.coenegrach/video/7325409101809290529</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1705579728</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2024-01-18 04:08:48</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>#openvld #niksmoetallesmag  #doejeeigending  #selfcontrol  @OpenVld</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>steven.coenegrach</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>7.319415444996132e+18</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@steven.coenegrach/video/7319415444996132128</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1704184244</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2024-01-02 00:30:44</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Wij gaan Vlaanderen niet op pauze zetten totdat de natuur zich herstelt heeft we gaan de twee trajecten samen lopen we gaan innoveren en onze industrie we gaan werkgelegenheid creëren de volgende jaren en we gaan de stikstofdepositie verminderen zodat de natuur kan herstellen we duwen Vlaanderen niet op pauze we doen dat heel bewust en we hebben dat goed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>steven.coenegrach</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>7.318022028164861e+18</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@steven.coenegrach/video/7318022028164861216</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1703859787</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2023-12-29 06:23:07</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>steven.coenegrach</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>7.318021305352097e+18</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@steven.coenegrach/video/7318021305352097057</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1703859618</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2023-12-29 06:20:18</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>#vlaamsbelang  #vlaamsparlement  #businessmodel</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>want die wanhoop van daar bij de boer de onde reddering bij de ondernemers in Vlaanderen chaos in de politiek dat is uw businessmodel dat is het model waarop u verkiezingen denkt te winnen de toekomst van de mensen interesseerde niet hun stem op 9 juni dat is wat uw interesseert</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7.378135845045374e+18</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7378135845045374240</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1717856126</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2024-06-08 07:15:26</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Demain, c'est le grand jour ! Voici le recap final de la campagne ! 💙 Morgen is het zo ver! Bij deze de laatste terugblik op de campagne! 💙</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>toi qui fait peur dans ton vécu love me too you are the stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>7.377747052270276e+18</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7377747052270275873</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1717765602</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2024-06-07 06:06:42</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>comment voter dimanche nous irons tous je l'espère au bureau de vote je suis quatrième sur la liste 2 Mr à la chambre et vous savez qu'on vote trois fois Europe chambre région dans cet ordre là alors si vous habitez en périphérie Drogenbos Linkebeek Kraainem reason Beckham Rhode-Saint-Genèse ou Wemmel des six communes à facilités vous pouvez aussi voter pour moi et pour ma liste comment faire on vous demandera d'abord de choisir votre arrondissement Russell ou Vlaams brave choisissez Russell si vous voulez me soutenir prenez la liste 2 colorier la petite boule à côté du numéro 4 et soutenez aussi mes collègues vous pouvez évidemment voter pour plusieurs personnes sur une même liste mais évitez s'il vous plaît de voter pour la case de tête c'est à dire le petit carré tout au dessus colorier vraiment les boules à côté des noms des personnes voilà merci à ceux qui nous soutiendront et merci à tous les autres d'aller voter quel que soit le parti tant que ce ne sont pas les extrêmes l'extrême gauche ou l'extrême droite vraiment c'est une élection cruciale</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>7.377060780400741e+18</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7377060780400741665</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1717605815</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024-06-05 09:43:35</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>7.376692031470587e+18</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7376692031470587168</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1717519961</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2024-06-04 09:52:41</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>7.376534571317202e+18</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7376534571317202208</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1717483299</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2024-06-03 23:41:39</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>7.375954473480506e+18</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7375954473480506656</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1717348236</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2024-06-02 10:10:36</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>7.375607370757459e+18</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7375607370757459232</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1717267418</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2024-06-01 11:43:38</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>7.374536582772149e+18</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7374536582772149536</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1717018110</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2024-05-29 14:28:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>7.373695397811719e+18</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7373695397811719457</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1716822251</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2024-05-27 08:04:11</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7.372990811669073e+18</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7372990811669073184</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1716658204</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2024-05-25 10:30:04</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>7.371900736059231e+18</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7371900736059231520</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1716404400</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2024-05-22 12:00:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>7.370678865628302e+18</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7370678865628302624</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1716119912</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2024-05-19 04:58:32</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>7.369952204402331e+18</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7369952204402330912</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1715950722</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2024-05-17 05:58:42</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>7.369285109343669e+18</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7369285109343669537</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1715795403</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2024-05-15 10:50:03</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>7.368513347404303e+18</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7368513347404303648</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1715615714</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2024-05-13 08:55:14</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>7.368136991147412e+18</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7368136991147412768</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1715528086</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2024-05-12 08:34:46</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>alexia.bertrand04</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>7.36630151577194e+18</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alexia.bertrand04/video/7366301515771940129</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1715100731</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2024-05-07 09:52:11</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>7.195146930760994e+18</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7195146930760994054</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1675250695</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2023-02-01 03:24:55</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>7.19077220686188e+18</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7190772206861880582</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1674232125</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2023-01-20 08:28:45</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>7.186930079144938e+18</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7186930079144938758</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1673337571</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2023-01-09 23:59:31</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>7.179874052960439e+18</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7179874052960439557</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1671694703</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2022-12-21 23:38:23</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>7.173180586222276e+18</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7173180586222275845</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1670136269</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2022-12-03 22:44:29</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>7.168790754179943e+18</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7168790754179943685</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1669114173</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2022-11-22 02:49:33</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>7.15996419251723e+18</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7159964192517229829</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1667059076</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2022-10-29 08:57:56</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>7.153632550198496e+18</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7153632550198496517</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1665584875</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2022-10-12 07:27:55</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>7.142963462228954e+18</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7142963462228954374</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1663100784</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2022-09-13 13:26:24</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>7.131731787591601e+18</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7131731787591601413</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1660485706</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2022-08-14 07:01:46</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>7.122700689490431e+18</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7122700689490431238</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1658382994</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2022-07-20 22:56:34</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>7.116207599502069e+18</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7116207599502068997</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1656871200</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2022-07-03 11:00:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>7.115372644215623e+18</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7115372644215622918</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1656676795</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2022-07-01 04:59:55</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>7.106542430350085e+18</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7106542430350085381</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1654620851</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2022-06-07 09:54:11</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>7.103584087675342e+18</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7103584087675342086</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1653932057</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2022-05-30 10:34:17</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>egbertlachaert</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>7.084949749022887e+18</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@egbertlachaert/video/7084949749022887173</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1649593411</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2022-04-10 05:23:31</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>7.378080011338681e+18</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7378080011338681632</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1717843124</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2024-06-08 03:38:44</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>7.378078867346574e+18</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7378078867346574625</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1717842860</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2024-06-08 03:34:20</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>7.378076715190341e+18</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7378076715190340897</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1717842359</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2024-06-08 03:25:59</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>7.378075047409307e+18</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7378075047409306912</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1717841969</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2024-06-08 03:19:29</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>7.37807058358346e+18</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7378070583583460640</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1717840932</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2024-06-08 03:02:12</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>7.378068681189805e+18</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7378068681189805345</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1717840487</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2024-06-08 02:54:47</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>7.378063283800067e+18</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7378063283800067361</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1717839232</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2024-06-08 02:33:52</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>7.378057634055736e+18</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7378057634055736609</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1717837917</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2024-06-08 02:11:57</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>7.378051612121648e+18</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7378051612121648417</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1717836517</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2024-06-08 01:48:37</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>7.377498154586918e+18</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7377498154586918176</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1717707650</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2024-06-06 14:00:50</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>7.376654411063397e+18</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7376654411063397665</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1717511205</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2024-06-04 07:26:45</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>7.376651177221508e+18</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7376651177221508385</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1717510450</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2024-06-04 07:14:10</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>7.376636418535312e+18</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7376636418535312672</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1717507014</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2024-06-04 06:16:54</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>7.375936614519868e+18</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7375936614519868704</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1717344076</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2024-06-02 09:01:16</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>7.37593614608322e+18</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7375936146083220768</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1717343969</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2024-06-02 08:59:29</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>7.374848287066656e+18</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7374848287066656033</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1717090683</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2024-05-30 10:38:03</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>7.374837838577405e+18</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7374837838577405217</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1717088247</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2024-05-30 09:57:27</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>7.374083786935471e+18</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7374083786935471392</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1716912683</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2024-05-28 09:11:23</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>7.37252665586626e+18</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7372526655866260769</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1716550139</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2024-05-24 04:28:59</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>7.371061416914193e+18</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7371061416914193696</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1716208983</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2024-05-20 05:43:03</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>7.37038039183801e+18</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7370380391838010657</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1716050416</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2024-05-18 09:40:16</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>7.370379451198131e+18</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7370379451198131489</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1716050197</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2024-05-18 09:36:37</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>7.368513686467562e+18</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7368513686467562785</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1715615792</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2024-05-13 08:56:32</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>7.367764373688929e+18</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7367764373688929568</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1715441332</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2024-05-11 08:28:52</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>7.367290446596279e+18</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7367290446596279584</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1715330983</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2024-05-10 01:49:43</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>7.366592019294211e+18</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7366592019294211360</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1715168372</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2024-05-08 04:39:32</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>7.366508109960859e+18</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7366508109960858912</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1715148843</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2024-05-07 23:14:03</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>elsampe1</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>7.362974330042486e+18</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@elsampe1/video/7362974330042486048</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1714326058</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2024-04-28 10:40:58</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>willemfrederik</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>7.378169112842833e+18</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@willemfrederik/video/7378169112842833185</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1717863903</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2024-06-08 09:25:03</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>willemfrederik</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>7.377688561216228e+18</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@willemfrederik/video/7377688561216228640</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1717751994</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2024-06-07 02:19:54</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>willemfrederik</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>7.377459519317691e+18</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@willemfrederik/video/7377459519317691680</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1717698685</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2024-06-06 11:31:25</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>willemfrederik</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>7.376884970863775e+18</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@willemfrederik/video/7376884970863775009</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1717564894</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2024-06-04 22:21:34</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>willemfrederik</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>7.376327125286112e+18</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@willemfrederik/video/7376327125286112544</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1717435030</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2024-06-03 10:17:10</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>willemfrederik</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>7.376320977094856e+18</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@willemfrederik/video/7376320977094855968</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1717433600</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2024-06-03 09:53:20</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>willemfrederik</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>7.376320747775528e+18</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@willemfrederik/video/7376320747775528224</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1717433544</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2024-06-03 09:52:24</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>willemfrederik</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>7.375118810203917e+18</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@willemfrederik/video/7375118810203917601</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1717153700</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2024-05-31 04:08:20</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>willemfrederik</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>7.374905110943649e+18</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@willemfrederik/video/7374905110943649057</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1717103942</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2024-05-30 14:19:02</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>mercedesvanvolcem</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>7.376920198890196e+18</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mercedesvanvolcem/video/7376920198890196256</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1717573088</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2024-06-05 00:38:08</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>mercedesvanvolcem</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>7.372080814869319e+18</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mercedesvanvolcem/video/7372080814869318944</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1716446333</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2024-05-22 23:38:53</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>mercedesvanvolcem</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>7.371590564539551e+18</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mercedesvanvolcem/video/7371590564539551008</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1716332184</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2024-05-21 15:56:24</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>mercedesvanvolcem</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>7.371587957569965e+18</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mercedesvanvolcem/video/7371587957569965344</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1716331578</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2024-05-21 15:46:18</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>mercedesvanvolcem</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>7.370421943691922e+18</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mercedesvanvolcem/video/7370421943691922721</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1716060089</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2024-05-18 12:21:29</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>mercedesvanvolcem</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>7.370421322809101e+18</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mercedesvanvolcem/video/7370421322809101600</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1716059948</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2024-05-18 12:19:08</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Goedemorgen in deze tijd zijn eh vrijheden heel belangrijk en zeker Van wie houdt omdat riep de universele is Ik vind het dan ook heel belangrijk en zeker en huidige tijden waar vrijheden onder druk staan dat ze vandaag eh op 17 mei drie regenboog banken hebben we gepraat op een unieke plek meer bepaald bij de ingang van het mengen Waterpark het minder Waterpark is een diepvries Park en wij vinden in Brugge dat iedereen die dat wel handje in hand open dat hij niet kon bank te zijn en dat je volledig jezelf kan zijn niet steeds mooier dan in een stad te leven voor mensen gelukkig zijn</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>mercedesvanvolcem</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>7.331353950215622e+18</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mercedesvanvolcem/video/7331353950215621920</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1706963867</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2024-02-03 04:37:47</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>mercedesvanvolcem</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>7.305405795435417e+18</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mercedesvanvolcem/video/7305405795435416865</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1700922342</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2023-11-25 06:25:42</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>brede maar ik vind wel een terecht met alle groen wat ontstaan is de laatste tijd vooral als je de stad in rijdt Lange straat moet je eigenlijk steeds groene worden En wij hebben de verzuchting Waarom kan dat niet</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>7.378185559069494e+18</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7378185559069494560</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1717867700</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2024-06-08 10:28:20</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Er is één reden waarom je wel voor Open Vld moet stemmen vrijheid vrij om te zijn wie wil zijn voor hem graag te zien wie er graag wil zien vrij om je eigen leven te leiden waarbij niemand u Allerhande regeltjes moet opleggen dat is iets waar wij liberale altijd voor gevochten hebben en zullen blijven doen En daarom moet je wel op Open Vld stemmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>7.37818035200464e+18</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7378180352004640032</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1717866488</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2024-06-08 10:08:08</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>7.377754632535281e+18</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7377754632535280929</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1717767368</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2024-06-07 06:36:08</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>ga zondag niet stemmen niet niet als je vindt dat ons land teveel vrij heeft Dat regelt is mogen bijkomen verplichtingen mogen bijkomen worden verplichte legerdienst voor alle 18-jarige zondag niet stemmen als je vindt dat er ook nog wat belastingen mogen bijkomen nog niet nog niet genoeg belastingen betalen en ga zondag niet stemmen als je vindt dat dit land eigenlijk kapot moet dat het moet splitsen ga zondag wel als je vindt er meer vrijheid moet komen minder regeltjes om te zijn wie je bent bijvoorbeeld maar bijvoorbeeld ook om onbeperkt te kunnen bijverdienen als jobstudent ga zondag ook stemmen als je vindt dat er meer mensen aan het werk moeten in plaats van meer belastingen en ga zondag zeker stemmen als je vindt de politie na de verkiezingen meteen aan de slag moeten gaan om met tenen regering te vormen die de problemen van de mensen aanpakt ga dan zeker stemmen en stem dan op Open Vld</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>7.377654006186806e+18</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7377654006186806561</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1717743939</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2024-06-07 00:05:39</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Waarom moeten de mensen op Tom ongena stemmen Weet jij ik ehm ik ben zo aan de militair En weet je wat dat betekent dat je een doener zijt niet teveel babbelen maar gewoon ik ben iemand die zaken aanpakt die ook durf heeft hè Ik ben voorzitter gewoon van de partij een moeilijke momenten en dan ben het teamspeler Ik weet dat je enkel maar resultaat boekt als je samenwerkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>7.377329457033498e+18</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7377329457033497888</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1717668373</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2024-06-06 03:06:13</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>kiezen voor Open Vld is kiezen voor meer mensen aan het werk in plaats van meer belastingen bij ons geen belastingplan maar een groeiplan Wij kiezen voor een vormingen voor meer mensen aan het werk want enkel Zo kunnen we onze pensioenen onze gezondheidszorg dan blijven betalen alleen zo kunnen we kunnen onze welvaart behouden en versterken als het gaat over de portemonnee van het als het gaat over toen groeien van onze economie dan kan je maar bij een partij zijn bij ons liberale bij ons overkomen</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>7.376548906399845e+18</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7376548906399845665</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1717486641</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2024-06-04 00:37:21</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>wij kunnen onmogelijk samenwerken bij Vlaams belang als ik nu Kijk hoe de laatste dagen en Gelukkig komt dat ook meer en meer aan de oppervlakte hoe dat zei ja eigenlijk kijken naar mensen uit de Holy be gemeenschap hoe dat zij kijken naar eten ze verder uza kijken naar vrouwen hè je moet voor u 30e moet je kinderen Baaren gaat dan zeg ik en wat is dat Is dat is van dat is ook dat is echt niet meer van deze tijd en dat bots echt tegen mijn vader een partij die vrouwen terug aan de haard wil die kliklijn wilt organiseren we in het onderwijs die geleerd Krachten die hun mening niet voorkomen de VRT hè wilt eh droog maar dat is echt omdat ze de kritische dat kan ik niet mee samen</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>7.376203547513474e+18</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7376203547513474336</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1717406230</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2024-06-03 02:17:10</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>we moeten de mensen nu toch ook niet wijsmaken dat wij als klein landje het migratie probleem gaan oplossen gemoed op een Europees niveau en ik vind dat migratie pact is een goede stap in de juiste richting zalm voldoende zijn dat zal moeten blijken maar wat doet dat migratie pakt dat zorgt voor een strenge controle aan de buitengrenzen dat die deur die voordeur dat die kleine wordt en ja ik vind het jammer dat je dat kunt afkopen We zullen zien wat er gebruikt tot ik hoor hem heel graag spreken over uitwijzing maar hoe kun jij iemand uitwijzen plant van heg komt Sanne midden vinger opsteekt de enige manier om daar druk op te zetten om die landen van herkomst is juist met een Europees migratie pact waarbij we bijvoorbeeld Handels akkoorden dat je met die landen dat je dat koppelt aan een verplicht terug naar zijn dus hoe dat je draait of keert meneer van je luistert wel alleen gaan wij dat niet oplossen we hebben zo migratie Zullen we zien ons voldoende werk maar daar zitten de juiste stappen zitten er wel degelijk een</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>7.375082892164156e+18</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7375082892164156704</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1717145308</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2024-05-31 01:48:28</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>gruw toch ook wel van het idee dat geklikt lijnen gaat krijgen in Vlaanderen voor leerkrachten die een mening verkondigen die niet past in uw kraam meneer van Grieken wat de lynx is wat wat betekent dat dan eigenlijk Nederlands die aan leerlingen vraagt van wilt gij een boek van Tom LAN wa lezen dat mag niet meer een andere leerkracht die zegt geschiedenis Ik ga met mijn leerling en ik ga met mijn studenten ga ik eens voor naar de film van Will kijken Dat mag ook allemaal niet meer want dat is allemaal ver Samuel Walk IQ daarvan we eindigen in een samenleving waar dat blijkbaar vrijheid van meningsuiting betekent enkel mijn mening die mag vrij gezegd worden en elke andere mening die moeten we verbieden</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>7.374827771052183e+18</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7374827771052182816</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1717085901</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2024-05-30 09:18:21</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>kan Jo Holiday of ongewenst zwanger dan laten we je voorlopig met rust voorlopig hè Dat is waar Tom Van Grieken de voorzitter van Vlaams belang Vandaag heeft gezegd Nee ik zal niet raken aan die rechte want er is toch geen meerderheid voor verstaat Als je mij zou laten doen dan zou je nogal wat zien dan gaan die rechte voor Holy Beach dan gaan die op de schop dan gaan we abortus wat eigenlijk moord is dan gaan we dat verbieden we weten dat ook overal waar extreem rechts aan de macht is gekomen heeft me de rechten van Holy bus ingeperkt heeft men abortus ingeperkt dan mogen we bij ons niet laten gebeuren wij liberale van Open Vld wij verzetten ons haar tegen en daarom willen we die rechte ook in de Grondwet verankeren want voor ons hè mag je zijn wie je bent en blijf je ook baas over eigen buik</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>7.374051267989048e+18</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7374051267989048608</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1716905112</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2024-05-28 07:05:12</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>We zijn eigenlijk de enige partij die bezig is met jouw portemonnee alle andere partijen van allemaal stellen allemaal heel veel nieuwe belastingen voor Wij zeggen Nederland naar belastingen genoeg in ons land moeten we nu hervormingen doorvoeren de caravan ons programma's groeiplan zodat er meer mensen aan het werk gaan zodat ze meer overhouden van hun woon zorg dat onze bedrijven ook Jobs kunnen creëren dat ze concurrentie krijgt houden niet de gemakkelijke weg van belastingbureau gingen dan zorgen dat we met de vormingen onze welvaart kunnen overhemd te houden</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>7.372952728814898e+18</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7372952728814898464</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1716649338</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2024-05-25 08:02:18</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>staat nog op de luchthaven van Zaventem de 2e economische groei Polen van ons land 64000 directe en indirecte Jobs die luchthaven die moeten we alle ruimte geven om te blijven groeien heel belangrijk voor onze economie heel belangrijk voor onze welvaart</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>7.37251870264802e+18</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7372518702648020256</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1716548287</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2024-05-24 03:58:07</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>wordt je 18 jaar Proficiat Dat moet je nu wel 6 maand naar het leger Dat is toch wat Sami Medi voorstel van cd&amp;v verplichte burgerdienst voor alle 18 jarige Wij zijn tegenover plichten burgerdienst vrijwillig ja als jongere jaren naar het leger willen gaan om eens te proberen om te zien of dat ze militair willen worden geen probleem laat mensen laat jongeren vrijwillig zo'n leger dienst doen maar we gaan er toch niet verplichten dat is zo jaren 80 zet een tijd van Stranger things gaan we nu toch niet meer doen wij mij Open Vld moeten vermogen verplichte leger of andere dienst voor 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>7.372204465404923e+18</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7372204465404923169</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1716475118</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2024-05-23 07:38:38</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Wij hebben op een Vld voor ons zijn twee kernwoorden een vrijheid Wij staan voor u vrijheid mensen niet teveel lastig vallen met regeltjes met belastingen maar ook vrij wie om te zijn wie je bent met de trouw met je dat wilt ook dat je baas bent over eigen buik dus rechter als abortus en zo zijn voor ons cruciaal en wij zijn optimisten wij doen niet meer aan al dat doen denken aan al dat negativisme Ja we staan voor grote uitdaging maar we kunnen dat aan de vooral optimistisch te blijven</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>7.371852222755393e+18</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7371852222755392801</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1716393107</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2024-05-22 08:51:47</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>hulp op heel veel dingen veel te veel regeltjes mensen die willen werken niet overal hè We gaan niet zo doen hè overuren Oh niet teveel overuren want we gaan misschien eens op van een andere afpakken klopt langs geen kanten meer studenten we gaan studenten toch niet toelaten dat die onbeperkt uren kloppen want je had zou willen zijn studies kunnen dan denk ik mensen laat die mensen toch vrij laat die toch zelf beslissen of dat ze nu de tijd willen steken en studies of een of een werken dus veel van die regeltjes die moeten we op de schop brengen maar zo kan beginnen</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>7.369527990448868e+18</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7369527990448868641</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1715851962</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2024-05-16 02:32:42</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>We hebben een heel duidelijke Focus koopkracht economie welvaart daar moeten we volop op inzetten en dat is als je daar als je zocht zo een goed draaiende economie met bedrijven die kunnen groeien Jobs kunnen creëren mensen die aan de slag kunnen gaan dat is de enige manier om meer middelen te hebben voor al die andere thema's te gebruiken</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>7.369227692736138e+18</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7369227692736138528</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1715782037</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2024-05-15 07:07:17</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>7.368901622312881e+18</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7368901622312881441</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1715706114</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2024-05-14 10:01:54</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>regenboogvlaggen horen niet thuis op een voetbalveld dat is wel Barbara Pas heeft gezegd politica voor Vlaams belang Wij zijn het daar compleet met oneens zeker nu zeker nu dat blijkt dat een op twee homo's en lesbiennes schrik hebben om hand in hand over straat te gaan schrik om gepest te worden misschien zelfs aangevallen te worden Zo moment hè Wat doe je het meer regenboogvlaggen uithangen maar Vlaams belang die willen dat niet natuurlijk Kijk maar wat bijvoorbeeld extreemrechtse premier gedaan heeft in Italië het eerste wat hij daarmee deed dat was de rechter van homo's en lesbiennes om bijvoorbeeld een kind te adopteren Daar rechts afgeschaft dan mogen we hier niet laten gebeuren wij Open Vld Wij willen de vrijheden hè van mensen ook van homo's en lesbiennes hè Wij willen die beschermen Want in dit land hè mag je zijn wie je wil zijn</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>7.368383401511947e+18</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7368383401511947553</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1715585468</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2024-05-13 00:31:08</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Wij stappen enkel en een regering laat me daar heel duidelijk en zijn we stappen enkele in de regering die echt werk maakt van mensen die werken beter belonen het verschil tussen niet werken en werken moet €500 worden we hebben dat als eerste partij hebben we de op tafel gelegd hebben we dat vorig jaar helemaal beseffen ik stel vast de andere partijen waar ons beginnen over tegen onze voorstel beginnen oor te nemen Ja dat was dat mij natuurlijk gelukkig En dat betekent laat ons er dan ook weg maken dus dat is voor ons een absoluut</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>7.367005904954248e+18</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7367005904954248481</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1715264733</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2024-05-09 07:25:33</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>uit de NAVO treden dat is dat is toch gewoon moeten we niet in Europa meer van afwerken hadden we de NAVO niet gehad dan waren we inderdaad nu allemaal communist Allez tegen ons wil dat was u een droom gerealiseerd maar dan leefden we allemaal in de miserie hè We hebben dat gezien Hey ik heb tot mijn 18 jaar in Duitsland gewoon mijn vader was bij ons met die tijger We hebben daar mijn NAVO leger voor gezorgd dat wat de miserie die men in Polen en Hongarije in oost-europa had dat hij niet bij ons omdat ze 30 jaar geleden echt waanzin wat u doet met zo'n Play dooie meneer gegeven dat is die een donker rode loper uitrollen voor Poetin Jij bent echt Ik vind het echt niet in mee en ik begrijp uw punt want die van meegaan tegen het Veroordeel van de Russische inval in Oekraïne daar heb je ook dat reptiel gestemd uw partij of dat je het Vlaams parlement tegenstander Ik heb daar een normale is normen nodig</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>tomongena</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>7.36662771129867e+18</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tomongena/video/7366627711298669856</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1715176682</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2024-05-08 06:58:02</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>zet geen honger Dan 15 jaar dan moet ge nu onmiddellijk stoppen met kijken en gedaan sleuth geen sociale media meer voor jongeren onder de 15 dat is wat sommige in Frankrijk voorstellen We hebben een zot idee maar jammer genoeg hè zijn er in ons land die gaat ook een goed idee vinden van vooruit Ja goed idee verbieden Hoe gaat jouw controleren zaterdag in de politie op WhatsApp sturen gaat de boetes geven jongeren die op tiktok durven zitten daar werkt toch niet weet wat moeten doen jongeren verstandig leren omgaan met sociale media en dat bijvoorbeeld leren op school dan moeten we doen in plaats van te verbieden</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>goedeleliekens</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>7.37773735435995e+18</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@goedeleliekens/video/7377737354359950624</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1717763345</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2024-06-07 05:29:05</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>heb je een seksueel opvoeding gekregen Nee dat wist ik van mijn eigen Hoezo dat wisten van uw eigen als kind weinig en vindt u dat de jeugd nu veel seksuele opvoeding zou moeten krijgen Want je ziet ze hebben dat toch wel langs een school in brand gestoken daarvoor hè Ja dat heb ik niet gevolgd eigenlijk maar ja die ouders die vonden dat hun kinderen op school geen seks willen opvoeding moeten krijgen omdat daar ook over homoseksualiteit en zo gesproken wordt Ja vind ik zonde en wij met ons kinderen doen dan wel bijvoorbeeld ja voor sexueel opvoering heb jij gekregen de de Basic is dat de Basic leggen mijn vrouw kindje en of wat is een reactie Wat is een orgasme gewoon die dingen die wel ja die dingen wel ja maar nooit echt van mijn mijn vrouw dat niet Nee want dan mogen ze wel geven vind ik dat mocht toch iets gemeen zijn dat is ook een katholiek onderwijs dus het was redelijk droog dus eh en dat is niet goed droog hè Nee dat is echt goed verder over seksueel plezier gesproken en operator over seksueel plezier uh ja is moeilijk hè Ja ja maar moeilijk gaat ook Ja Waarom reed het meer moet op school te geven toch Ik denk het wel belangrijk is</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>goedeleliekens</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>7.377373251934162e+18</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@goedeleliekens/video/7377373251934162209</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1717678593</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2024-06-06 05:56:33</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Weet je hoe je eh geldig kan stemmen dat denk ik wel ja of de dingen en daar moet je de namen ook aan de kunde ook gewoon de namen aan de zolder hierboven Ja dat wil je dus zoek mijn bolleke hè Maar ik denk het wel geboden zijn zoeken hoe kan je geldig stemmen je moet geldig kunnen stemmen hè Ja je kan achter de naam een bolletje zetten en kan het dan bij verschillende partijen of moet dat bij een partij verschillende wat we geleerd vandaag zou Piet Huysentruyt stijgen eh ik ga dat gewoon stemmen op een partij hier kan ik eh verschillende Bollekes Ik ben echt verbaasd hoe weinig mensen dat weten hè voorlopig ik zeg van de gooien dat is goed Nee je moet niet van boven invullen moet zelf uw volksvertegenwoordiger kiezen als je van boven invult dan besliste partij Wii U volksvertegenwoordiger wordt hè op de papieren dat wij krijgen er staan geen Bollekes op die reclame en moeder dan een bootje op de zijkant op de naam is de meerdere je mocht er meerdere binnen een partij van boven uit en nog misschien voor een bepaalde persoon bijvoorbeeld en mag je dan hier En hier een bolletje zetten Ik zal voor een eh één partij dan gaan hè oftewel boven oftewel voor twee kandidaten hoeveel van die lijsten gaat het te zien krijgt het is gewoon op hè Ik loop dan een drie papier gaan krijgen hè denk ik Ja maar goed zoek met bolle</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>goedeleliekens</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>7.377041221824318e+18</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@goedeleliekens/video/7377041221824318753</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1717601262</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2024-06-05 08:27:42</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Wat vind jij ervan als twee mannen handen een hand lopen Ik heb daar geen problemen met de redelijke rem denken dat stuurt mij niet iedereen vrij kunnen zijn om te zijn wie die is om verliefd te worden op je dat die verliefd kan worden dan moet je dat gewoon negeren Ik vind dat niet goed en En wat zijn verliefd op elkaar geworden maar eh finger Till eh van een hele andere wereld zijn maar ze worden zo geboren hè ze worden ze kiezen daar niet voor u stel nu heb je nu omgeving geen homo of lesbische vrienden Ja ik heb er in een gaming Ik ga naar liever niet mee om zelfs liever niet met jou want wat zou dat kunnen uitmaken die ruiken toch niet raar nee maar eh kip lever eh ok bonne nuit</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>goedeleliekens</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>7.376330601755889e+18</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@goedeleliekens/video/7376330601755888929</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1717435809</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2024-06-03 10:30:09</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>8 op de 10 verkrachtingen gebeuren door iemand die het slachtoffer kent achter de tien is veel hè langs nog hè dat 14-jarig meisje slachtoffer van een groeps verkrachting in Kortrijk was zeker Wie was de aanstoken haar vriendje en dat zijn vooral meisjes die slachtoffers maar en dat is een heel belangrijke ook Jongens worden slachtoffer want voor hen is het nog moeilijker vaak om aangifte te doen en hoe komt dat eigenlijk dat zo weinig meisjes en jongens aangifte gaan doen 90% zegt eigenlijk niks hè of dat ze zich schul Ze denken dat ze het zelf gezocht hebben Ja ik had maar niet zoveel moeten drinken Ik heb de verkeerde signalen uitgestuurd Het is een toffe peer van onze vrienden klik wil de sfeer die verknoeien ik wil niet de flauw doos uithangen gedaan Het moet er meegedaan zijn Het is niet jouw schuld stinkt dat uw kop Het is je eigen lichaam en je beslist zelf wie er aankomt op elk moment en op elke plaats dus als er McQueen 's nachts bij je in de tent kruipt en je kan niet en geven dat je dat eigenlijk niet wilt of je Versteeg En zoals een zeester dan een geld het als verkrachting 15 jaar cel kan je daarvoor krijgen 15 jaar en je mag dat gerust op mij steken Ik ben de schuldig Ik heb meegewerkt aan het nieuwe seksuele straffe het boek en daarin staat die toestemming centraal dus voor de beste seks eerst blabla dan boem boem boem</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>goedeleliekens</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>7.375969377071418e+18</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@goedeleliekens/video/7375969377071418656</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1717351703</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2024-06-02 11:08:23</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>kan je je voorstellen dat er zoals van die stickers hè vonden niet toegelaten dat er ook zo'n stickers zou zijn homo's niet toegelaten en dat hij op de deur van café zijn restaurant hangen in Polen was dat zo dat kon je stickers bestellen en aangeven dat jouw zaak een no guay zo was ik natuurlijk in het parlement van mijn contact maken en Allez We zijn hier over Europa bezig hè ja Krijg ik dan te horen ja maar het gaat maar over de symboliek het is geen echt homo vrije zone ja toen kwam het stoom natuurlijk helemaal uit mijn oren hè Het nat oor de symboliek van zo'n sticker van de Walk Like antiche sfeer die dat oproept die die foute propaganda daar gaat het met over van de week in de krant nog hè de helft van de regenboog Community vermijd bewust om hand in hand te lopen op straat en spijtig genoeg is dat begrijpelijk hè want één op de zeven kreeg al te maken met geweld twee op de drie van hen werd op school gepest beledigd bedreigd omdat ze dus lgbtqi plus zijn wat zeg ik dan in de kiem smoren dat soort historisch gedachtegoed je wordt zo geboren net zoals je bijvoorbeeld met blond haar op donkere haar of roze en zelfs al zouden ze er wel voor kiezen de tapijt bij uw ergens eh ketel dat krijg je daar jeuk van en gij daar op een of andere manier een minder leuk leven door Eigenlijk bedoel ik Ah bemoei u mij lief is liefde en sexy seks dat mag ook hè zeker van mij en laat ons gaan voor een wereld waar iedereen mag kiezen wie die graag ziet en wij willen dus te laten sterkte</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>goedeleliekens</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>7.374819800914071e+18</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@goedeleliekens/video/7374819800914070816</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1717084047</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2024-05-30 08:47:27</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Moet jij nog vaak complimentjes aanvragen aan die van mij toch Ja dat is correct Ja en dan vreemde vrouwen of mensen vriendin Ik denk als je zelf aanvoelt dat het niet goed kan landen gewoon niet doen problemen mee gehad dit vind ik niet leuk dat er wel een keer bouwvakkers naar U Roepen of fluiten maar ja je moet dat gewoon negeren vind ik negeer ik ga terug als ze naar mij fluiten en dan ga ik trouwens schitterende uit een complimentje</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>goedeleliekens</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>7.374031822151241e+18</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@goedeleliekens/video/7374031822151240992</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1716900587</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2024-05-28 05:49:47</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>als u een hele moord familie drama huiselijk geweld Alpha zegt het gaat over vrouwen moord familiedrama familie Alé van de ja dat heeft daar toch niks mee te maken met zo'n gruwel en huiswerk is het ook niet hè Dat soort geweld maar ik vind echt dat het tijd wordt dat we dat dingen benoemen zoals ze zijn vrouwen moord feesten dat is waar het over gaat gepleegd door een partner of the ex partner omdat hij het niet kan verkopen Dat zijn vrouw dat hij een relatie wil beëindigen nooit voor Julia heel belangrijke message Wat heeft mijn keel boze reactie gestuurd dat ik een trut ben en een kutwijf want dat er ook mannen slachtoffer zijn waar absoluut en even verschrikkelijk en ook daar moeten we tegen optreden Julien kunnen dat gewoon een keer wel wat vriendelijker mededelen alstublieft 90% van dat soort geweld is gericht op vrouwen 76% van de gevallen door haar partner of ex-partner als een man wordt vermoord hè is dat maar een 6% van de gevallen zo en daarom in de kamer een stop Femmy siere wet gemaakt dat is een heel stappenplan om beter en ons sneller te kunnen ingrijpen om het te kunnen verwijderen met alarm knoppen opvang te huizen voor de vrouw voor de kinderen ook plaats waar de de dader kan geholpen worden iedereen moet geholpen worden dus ook de mannen en Julia juist zeg je nog dat de politie niets doet</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>goedeleliekens</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>7.373280726835383e+18</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@goedeleliekens/video/7373280726835383584</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1716725704</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2024-05-26 05:15:04</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>eigenlijk Ik zeg altijd is dat het glijmiddel naar een betere wereld voor iedereen Ja ik weet niet of je dat weet maar voor ik in de politiek eh ging was ik voor de You Win en beste er een reisde ik de wereld rond op de strijder voor vrouwenrechten Weet je wat daar essentieel voor is voor vrouwenrechten dit of een ander moderne anticonceptiemiddel natuurlijk als meisjes kunnen kiezen of ze kinderen krijgen en wanneer dan kunnen ze hun school afmaken want ja ongewenste zwangerschap dat is nog altijd een van de hoofdreden waarom ze stoppen dan kunnen ze later een goede Job krijgen dan zijn ze onafhankelijk we weten dan lopen ze ook minder kans op seksuele familiaal geweld als we onafhankelijk zetten Ja maar vooral de economie draait ook beter of wat een heel sneeuwballen effect aan positieve gevolgen ze worden er zelf beter van en de hele maatschappij wordt er beter van voor elke euro die geïnvesteerd in seksuele rechten waar Meisjes hè krijg je €100 terug waarom zeg ik dit nu allemaal voor de mensen die niet met zichzelf bezig zijn Maar die ook wel een fak geven om het wel zeg maar vrouwen hier in België en in de rest van de wereld denk daar bij de volgende verkiezingen is bijna</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>goedeleliekens</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>7.37219824937501e+18</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@goedeleliekens/video/7372198249375010081</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1716473673</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2024-05-23 07:14:33</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Het ziet er maar zitten We zijn op de markt in Dilbeek gaat paar vragen stellen aan de mensen mag je vragen stellen dat er genoeg vrouwen in de politiek zijn dat mag altijd meer vrouwen thuis blijven Oei Ik Zit In de politiek zal het verschil zijn als er meer vrouwen in de politiek zitten Ik denk dat correcte een politicus denk nu wat dat goed in balans zou zijn en dat eh mevrouw en evenveel en goede zaken kunnen we vertellen en als de mannen even goed of beter beter even goed even goed gelijk dus op vrouwenstemmen Oké stem vrouw</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>goedeleliekens</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>7.372129308338441e+18</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@goedeleliekens/video/7372129308338441504</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1716457622</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2024-05-23 02:47:02</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>There is een interessant fenomeen namelijk dat steeds minder meisjes de pil gebruiken en dat is voor het eerst want een jaren is er altijd gestegen en nu voor het eerst daalt dat gebruik en dan met name op heel opvallend bij zeer jonge meisjes onder de 21 Ja dat te maken heeft met social media tiktok en Instagram Ja dat is puur vergif en dat is echt een een hormonale experiment misdaad is en dan zie je zo heel ostentatief die tiktok influencer zo veel strip weggooien voort zingen de kerk uit of de kalender zie je gezicht toch Gare ja of de kalender methoden hè Hebben ze een app op een telefoon daar steken ze allerlei informatie ik dat herken ik ik er al gezien dat dat is want nu is het veilig zo bij iemand die denkt het moment ga maar</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>goedeleliekens</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>7.372121568673156e+18</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@goedeleliekens/video/7372121568673156385</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1716455821</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2024-05-23 02:17:01</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>als we daar nu eens een leuk erotisch moment van maken en we zeggen zeg één keer per maand die lekkere plekjes en vlekjes mensen denken vaak ja maar ja huidkanker ziet aan de buitenkant weg en klaar maar dat wat Professor namens met ons ook mooi zijn van Kijk eens als een melanoom naar binnen gaat maakt hij rare sprongen dus we moeten die heel goed volgen en en behandelen</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>goedeleliekens</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>7.372120705510428e+18</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@goedeleliekens/video/7372120705510427937</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1716455616</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2024-05-23 02:13:36</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>men dyt ding Je kan met je moeder bellen Je zit dat erop en gaat toch gebeuren en dat is een heel goeie machine die werkt heel goed heel efficiënt dat is echt van Zero tot Oh my god op minder dan 2 minuten is zo efficiënt dat het te efficiënt wordt het is toch juist leuk als het een beetje duur is en een beetje opbouwt Dit is een steekvlam en een steekvlam is ook snel uitgedoofd Dus je focussen niet en we weten een van de probleem als vrouwen zeggen ik heb problemen met klaarkomen heeft dat te maken met zijn ze zijn af ze zijn al iets anders aan het denken</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>marianne.verhaert</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>7.37765566046654e+18</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@marianne.verhaert/video/7377655660466539809</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1717744334</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2024-06-07 00:12:14</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>laat maar ik heb ze nu toch laten groeien</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>marianne.verhaert</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>7.376203448917806e+18</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@marianne.verhaert/video/7376203448917806368</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1717406256</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2024-06-03 02:17:36</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>minder regels en sneller</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>marianne.verhaert</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>7.360996051316215e+18</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@marianne.verhaert/video/7360996051316215073</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1713865463</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2024-04-23 02:44:23</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>hysterie Secret Garden Hi i i i i i i you wanna Take me up at me what it is</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>marianne.verhaert</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>7.353277227292839e+18</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@marianne.verhaert/video/7353277227292839200</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1712068276</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2024-04-02 07:31:16</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>marianne.verhaert</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>7.340209073045966e+18</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@marianne.verhaert/video/7340209073045966112</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1709025622</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2024-02-27 01:20:22</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>marianne.verhaert</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>7.339859998828137e+18</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@marianne.verhaert/video/7339859998828137761</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1708944340</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2024-02-26 02:45:40</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>laurencelibert</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>7.357791128420191e+18</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@laurencelibert/video/7357791128420191521</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1713119250</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2024-04-14 11:27:30</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Hallo ik ben hier naar Kuringen naar de bossen met de generale repetitie voor de tandarts zondag 7 weken geleden gestart met trein gaat heel moeizaam maar ik hoop oprecht dat ik volgende week de eindstreep haalt We zullen zien en heel wat andere opties natuur Ik ben heel hardheid gaat halen we gaan er wel eens een doen dat is dat samen over eh over the finish komt en bij deze ook nog eens een uitdaging aan onze voorzitter Tom ongena die ook mee gaat lopen Het is mijn naam is niet elke van het sneller dan hem pijn</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>laurencelibert</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>7.171414495435296e+18</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@laurencelibert/video/7171414495435296006</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1669725059</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2022-11-29 04:30:59</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Sinterklaas gaat proberen het wereldrecord schoentjes zetten te breken aanstaande zondag 4 december in de namiddag Dus breng allemaal jullie schoentjes binnen en de schoentjes krijgen een volgend leven zodat ze niet weg hoeven gegooid te worden dus allemaal de schuld is binnen brengen in de loop van deze week tijdens de openingstijden van 206 in de tuin</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>laurencelibert</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>7.167387464309542e+18</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@laurencelibert/video/7167387464309542150</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1668787441</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2022-11-18 08:04:01</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>laurencelibert</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>7.159885522771414e+18</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@laurencelibert/video/7159885522771414278</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1667040761</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2022-10-29 03:52:41</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>you wanna picture of close For You Now You Got Me Now You Like Another One You Like This one</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>laurencelibert</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>7.156873365263748e+18</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@laurencelibert/video/7156873365263748357</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1666339443</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2022-10-21 01:04:03</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Who know I going with a Dancing hashtags And I have to thank you and Drunk In Love With You</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>laurencelibert</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>7.154797728667946e+18</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@laurencelibert/video/7154797728667946245</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1665856163</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2022-10-15 10:49:23</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>laurencelibert</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>7.154297868407377e+18</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@laurencelibert/video/7154297868407377157</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1665739787</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2022-10-14 02:29:47</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>TRANSCRIPTION_FAILED</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>laurencelibert</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>7.153965464463363e+18</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@laurencelibert/video/7153965464463363333</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1665662388</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2022-10-13 04:59:48</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Diana</t>
+        </is>
       </c>
     </row>
   </sheetData>
